--- a/backtest_runs/20260410_193731/by_symbol/CLCPS/CLCPS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/CLCPS/CLCPS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-4316.520000000004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>95683.48</v>
@@ -587,7 +587,7 @@
         <v>-359.7100000000083</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>95323.76999999999</v>
@@ -633,7 +633,7 @@
         <v>-1438.839999999985</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>93884.93000000001</v>
@@ -679,7 +679,7 @@
         <v>-19784.05000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>74100.87999999999</v>
@@ -817,7 +817,7 @@
         <v>-7913.619999999991</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>73021.75</v>
@@ -909,7 +909,7 @@
         <v>-2517.969999999994</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>75180.00999999999</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>75180.00999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-719.4200000000006</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>84892.17999999999</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>88129.57000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-5395.649999999997</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>86331.02000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-4676.229999999996</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>84532.47000000003</v>
@@ -1461,7 +1461,7 @@
         <v>-3597.100000000003</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>80935.37000000002</v>
@@ -1645,7 +1645,7 @@
         <v>-5395.649999999997</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>84532.47000000003</v>
